--- a/extenbooks/S711_extenbook.xlsx
+++ b/extenbooks/S711_extenbook.xlsx
@@ -13468,7 +13468,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -14902,11 +14902,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14929,112 +14929,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Figure 7.21 — OECD Industry IROP Deviations, 1988–2003 (PPP-adjusted; OECD STAN 2003 + PWT 6.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S711_research.json", "adequacy_report": "Technical/docs/chapters/CH7_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S711_DPR.md", "epr": "Technical/docs/series/S711_EPR.md", "loader": "Technical/code/L01_loaders/L01_S711_load.py", "processor": "Technical/code/P02_processors/P02_S711_construct.py", "validator": "Technical/code/V03_validators/V03_S711_validate.py", "processed": "Technical/data/processed/S711.parquet", "chopped_csv": "Technical/chopped/S711.csv", "extenbook_xlsx": "Technical/extenbooks/S711_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S711-A"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_2008_APPENDIX_7_2_OECD_IROP"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>content_type</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>time_series</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>extension_status</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>feasible_deferred</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S711_extenbook.xlsx
+++ b/extenbooks/S711_extenbook.xlsx
@@ -13415,7 +13415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A147"/>
+  <dimension ref="A1:A187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -13618,7 +13618,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| **S711-A** | 1988–2005 | Appendix 7.2 iropOECDPPP — 27 OECD industries (ISIC Rev 3) byte-exact | rate deviation (decimal; industry IROP minus All-Industries average IROP, PPP-adjusted International Dollars) |</t>
+          <t>| **S711-A** (subseries — one data line within S711) | 1988–2005 | Appendix 7.2 iropOECDPPP — 27 OECD industries (ISIC Rev 3 = International Standard Industrial Classification, Revision 3) byte-exact | rate deviation (decimal; industry IROP minus All-Industries average IROP, PPP-adjusted International Dollars) |</t>
         </is>
       </c>
     </row>
@@ -13655,14 +13655,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1. Country-industry GFCF and GOPS from OECD STAN 2003 vintage (currently irrecoverable; Shaikh's pre-computed sheet stands as byte-exact record).</t>
+          <t>1. Country-industry GFCF (Gross Fixed Capital Formation) and GOPS (Gross Operating Surplus) from OECD STAN 2003 vintage (currently irrecoverable; Shaikh's pre-computed sheet stands as byte-exact record).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2. PPP-convert to International Dollars via PWT 6.2.</t>
+          <t>2. PPP (purchasing-power-parity)-convert to International Dollars via PWT 6.2 (Penn World Table 6.2).</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8. **No WEQ adjustment** (book p. 859 V.2: international data did not allow removal of self-employed income).</t>
+          <t>8. **No WEQ (wage-equivalent) adjustment** (book p. 859 V.2: international data did not allow removal of self-employed income).</t>
         </is>
       </c>
     </row>
@@ -13836,7 +13836,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>- **CD2 legacy ID**: `S038`</t>
+          <t>- **CD2 legacy ID** (identifier in CD2, the predecessor build of this dataset): `S038`</t>
         </is>
       </c>
     </row>
@@ -13853,7 +13853,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>## Notation (plain-language key)</t>
         </is>
       </c>
     </row>
@@ -13863,194 +13863,210 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>- **S### / -A** — series identifiers in this project (e.g. S711); a trailing letter (e.g. S711-A) marks a *subseries* — one data line within that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>- **DPR / EPR** — Data Provenance Record (this file) / Extension Provenance Record (its companion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>- **Phase N** — Anu Framework pipeline stages: Phase 4 = adequacy/readiness review, Phase 5 = ingestion, Phase 6 = extension, Phase 9 = visualization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>- **ROP** — (average) rate of profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>- **IROP** — incremental rate of profit: the return on newly added capital (the year-to-year change in profit divided by the new investment that produced it).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>- **PPP** — purchasing power parity (used here to convert to International Dollars).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>- **STAN** — OECD Structural Analysis database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>- **PWT** — Penn World Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>- **ISIC Rev 3 / Rev 4** — International Standard Industrial Classification, Revision 3 / Revision 4 (the UN industry-code scheme).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>- **WEQ** — wage equivalent: an imputed labour income for self-employed / proprietors, adjusted out of surplus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>- **GFCF** — Gross Fixed Capital Formation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>- **GOPS / GOS** — Gross Operating Surplus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>- **MAE** — mean absolute error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>- **Tolerance**: ±1.0% per cell (time_series default).</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>- **Expected MAE** against `iropOECDPPP` columns: 0.0 (verbatim).</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4">
+    <row r="101">
+      <c r="A101" s="4">
         <f>== EPR: S711_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t># S711 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>**Series**: S711 — Figure 7.21 — OECD Industry IROP Deviations, 1988–2003 (PPP-adjusted; OECD STAN 2003 + PWT 6.2)</t>
         </is>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `composite`</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>**Extension method**: Phase 5 = direct byte-exact from salvaged xlsx. Extension to 2023 = OECD STAN 2025 + PWT 10.01 (deferred per Phase 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch7-fanout</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>**Related**: `S711_DPR.md`</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>## 1. Why this series is extendable in principle</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>`content_type = time_series`. OECD STAN continues; PWT continues. But the **2003 vintage** Shaikh used is gone, and the **country list** has dropped from ~30 to 18. Extension is feasible only with explicit Concept Match Justification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>## 2. Construction classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>`composite`. The series is built from country-industry primaries via PPP conversion, country aggregation, ratio formation, and cross-industry deviation. Anti-degradation forbids splicing the derived deviation; extension must re-fetch components and re-compute.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>## 3. Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>### 3.1 Phase 5 byte-exact (this wave)</t>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>**Construction classification**: `composite`</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>**Extension method**: Phase 5 = direct byte-exact from salvaged xlsx. Extension to 2023 = OECD STAN 2025 + PWT 10.01 (deferred per Phase 4)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>INPUTS: Appendix7_iropOECDPPP.xlsx (SalvagedInputs)</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>L01: read the `_Dev` columns + level columns</t>
+          <t>**Author**: opus-subagent-ch7-fanout</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>P02: emit long-form parquet</t>
+          <t>**Related**: `S711_DPR.md`</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>V03: compare to xlsx; expect MAE ≈ 0</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14076,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>### 3.2 Phase 6 extension (deferred — separate wave)</t>
+          <t>## 1. Why this series is extendable in principle</t>
         </is>
       </c>
     </row>
@@ -14070,63 +14086,47 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>`content_type = time_series`. OECD STAN (Structural Analysis database) continues; PWT (Penn World Table) continues. But the **2003 vintage** Shaikh used is gone, and the **country list** has dropped from ~30 to 18. Extension is feasible only with explicit Concept Match Justification.</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>INPUTS: OECD STAN 2025 GFCF + GOPS via Data Explorer + PWT 10.01 PPP factors</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CONSTRUCTION:</t>
+          <t>## 2. Construction classification</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - ISIC Rev 3 → Rev 4 industry crosswalk (Phase 5 metadata deliverable)</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 30 → 18 country set discontinuity documented in Concept Match Justification</t>
+          <t>`composite`. The series is built from country-industry primaries via PPP conversion, country aggregation, ratio formation, and cross-industry deviation. Anti-degradation forbids splicing the derived deviation; extension must re-fetch components and re-compute.</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - apply 3+ country rule (book p. 859 V.4)</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - aggregate-before-ratio (book p. 859 V.7)</t>
+          <t>## 3. Method</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - NO WEQ adjustment (book p. 859 V.2)</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>### 3.1 Phase 5 byte-exact (this wave)</t>
         </is>
       </c>
     </row>
@@ -14136,112 +14136,128 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Concept Match Justification (required for the eventual extension wave):</t>
+          <t>The scripts named below are the per-series loader (`L01`), processor (`P02`), and validator (`V03`).</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>- **OECD STAN 2003 → 2025**: continuous database family; coverage drop 30→18 is a documented OECD policy change, not a methodology break; included industries' GFCF/GOPS definitions are stable across vintages within ISIC Rev 3→4 crosswalk.</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>- **PWT 6.2 → 10.01**: continuous academic project (Penn World Table); PPP methodology evolved but cross-country aggregate effects largely wash out per CD2 MAE = 0.04 on the overlap window.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>INPUTS: Appendix7_iropOECDPPP.xlsx (SalvagedInputs)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>## 4. Proxies</t>
+          <t>L01: read the `_Dev` columns + level columns</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>P02: emit long-form parquet</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>**None.** All substitutions are within-database-family.</t>
+          <t>V03: compare to xlsx; expect MAE ≈ 0</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>## 5. Synthetic data</t>
-        </is>
-      </c>
+      <c r="A134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>### 3.2 Phase 6 extension (deferred — separate wave)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>**None.**</t>
-        </is>
-      </c>
+      <c r="A136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>## 6. Failure modes</t>
+          <t>INPUTS: OECD STAN 2025 GFCF + GOPS via Data Explorer + PWT 10.01 PPP factors</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION:</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>| Failure | Action |</t>
+          <t xml:space="preserve">  - ISIC Rev 3 → Rev 4 industry crosswalk (Phase 5 metadata deliverable)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t xml:space="preserve">  - 30 → 18 country set discontinuity documented in Concept Match Justification</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>| Salvaged xlsx missing | FAIL — re-fetch from Wayback snapshot |</t>
+          <t xml:space="preserve">  - apply 3+ country rule (book p. 859 V.4)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>| OECD STAN 2025 endpoint 4xx/5xx (extension wave) | Cache + retry; degrade extension |</t>
+          <t xml:space="preserve">  - aggregate-before-ratio (book p. 859 V.7)</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - NO WEQ adjustment (book p. 859 V.2)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -14251,7 +14267,243 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>Concept Match Justification (required for the eventual extension wave):</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>- **OECD STAN 2003 → 2025**: continuous database family; coverage drop 30→18 is a documented OECD policy change, not a methodology break; included industries' GFCF (Gross Fixed Capital Formation) / GOPS (Gross Operating Surplus) definitions are stable across vintages within ISIC (International Standard Industrial Classification) Rev 3→4 crosswalk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>- **PWT 6.2 → 10.01**: continuous academic project (Penn World Table); PPP (purchasing-power-parity) methodology evolved but cross-country aggregate effects largely wash out per CD2 (the predecessor build of this dataset) MAE = 0.04 on the overlap window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>## 4. Proxies</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>**None.** All substitutions are within-database-family.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>## 5. Synthetic data</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>**None.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>## 6. Failure modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>| Failure | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>| Salvaged xlsx missing | FAIL — re-fetch from Wayback snapshot |</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>| OECD STAN 2025 endpoint 4xx/5xx (extension wave) | Cache + retry; degrade extension |</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>## 7. CD2 divergence pre-disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
           <t>CD2's `S038` used the same xlsx for the book period; RSCD's Phase 5 deliverable should match CD2 at MAE = 0 on 1988–2005. CD2's extension trajectory used OECD STAN 2025 + PWT 10.01 with crosswalk and reports MAE = 0.04 — ratified by Phase 4 as the eventual extension method.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>- **S### / -A** — series identifiers in this project (e.g. S711); a trailing letter (e.g. S711-A) marks a *subseries* — one data line within that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>- **DPR / EPR** — Data Provenance Record / Extension Provenance Record (this file).</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>- **Phase N** — Anu Framework pipeline stages: Phase 4 = adequacy/readiness review, Phase 5 = ingestion, Phase 6 = extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>- **L01 / P02 / V03** — the per-series load / process / validate scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>- **IROP** — incremental rate of profit: the return on newly added capital (the year-to-year change in profit divided by the new investment that produced it).</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>- **PPP** — purchasing power parity (used here to convert to International Dollars).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>- **STAN** — OECD Structural Analysis database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>- **PWT** — Penn World Table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>- **ISIC Rev 3 / Rev 4** — International Standard Industrial Classification, Revision 3 / Revision 4 (the UN industry-code scheme).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>- **WEQ** — wage equivalent: an imputed labour income for self-employed / proprietors, adjusted out of surplus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>- **GFCF** — Gross Fixed Capital Formation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>- **GOPS** — Gross Operating Surplus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>- **MAE** — mean absolute error.</t>
         </is>
       </c>
     </row>
@@ -14887,7 +15139,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:08:30.747059+00:00</t>
+          <t>2026-07-02T06:25:32.098186+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S711_extenbook.xlsx
+++ b/extenbooks/S711_extenbook.xlsx
@@ -15139,7 +15139,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:25:32.098186+00:00</t>
+          <t>2026-07-11T03:44:26.267953+00:00</t>
         </is>
       </c>
     </row>
@@ -15154,11 +15154,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15181,6 +15181,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2008_APPENDIX_7_2_OECD_IROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "PPP-adjusted OECD-wide incremental-rate deviation panel (28 industries) from Shaikh's Appendix 7.2 (OECD STAN 2003 vintage + Penn World Table 6.2 PPP). Average ROP not computable (capital stock too sparse), so IROP only \u2014 confirmed against KB ch07 p.305. Figure 7.21 caption, the PPP method, and the '~30 OECD countries' caveat verified verbatim against KB. Data ends 2003 (registry-correct, not a reproduction error). Display name updated to 1988\u20132003 to match the data; the registry/research '1988\u20132005' framing refers to the data vintage envelope.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S711_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S711_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Decision 0004: Ch7 figure not covered by Phase 2 candidate list; ported from CD2 S038. | year_range corrected 2026-07-02 (P29): registry claimed [1988,2005] but no extension data ships (chopped + book both end 2003; no extension block / -EXT subseries); reconciled to [1988,2003].</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rate deviation (decimal; industry IROP minus All-Industries average IROP, PPP-adjusted International Dollars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
